--- a/hotel_manager_forms/010_hotel_reopening_on_duty_form--hotel_manager_forms.xlsx
+++ b/hotel_manager_forms/010_hotel_reopening_on_duty_form--hotel_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hotel_reopening_on_duty_form</t>
+          <t>hotel_reopening_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reopen_hotel</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Current Reopening Status</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the current status of the hotel's reopening plan.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hotel_manager_forms</t>
+          <t>safety_training_completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Safety Training Completed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Has the hotel completed safety training for all employees?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>reopen_hotel</t>
+          <t>safety_measures</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Safety Measures</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe the safety measures in place to prevent the spread of COVID-19.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hotel_reopening_on_duty_form_description</t>
+          <t>number_of_guests</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>form_description</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Number of Guests</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estimate the number of guests expected to arrive during the reopening period.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>social_distance</t>
+          <t>number_of_employees</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>social_distance</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Number of Employees</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estimate the number of employees expected to be on site during the reopening period.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>safety_precautions</t>
+          <t>reopen_time_frame_duration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>safety_precautions</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Reopen Time Frame Duration</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estimate the duration of the reopening time frame.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>safety_equipment</t>
+          <t>goals_of_safety_measures</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>safety_equipment</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Goals of Safety Measures</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe the goals of the safety measures in place.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reopen_time_frame</t>
+          <t>safety_equipment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reopen_time_frame</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Safety Equipment</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Are there any safety equipment or tools that need to be purchased or updated?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reopen_date</t>
+          <t>safety_proocols</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>reopen_date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Safety Protocols</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Are there any specific safety protocols that need to be followed during the reopening period?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>safety_training_completed</t>
+          <t>number_of_guestrooms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>safety_training_completed</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Number of Guestrooms</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estimate the number of guestrooms available during the reopening period.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>prophets_employees</t>
+          <t>employee_testing_results</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>employees_on_site</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Employee Testing Results</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe the employee testing results.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,297 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>number_of_employees</t>
+          <t>reopen_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>number_of_employees</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Reopen Date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Provide the reopening date.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>reopen_time_frame_duration</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>reopen_time_frame_duration</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>number_of_guests</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>number_of_guests</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>number_of_guestrooms</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>number_of_guestrooms</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>reopen_time_frame</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>reopen_time_frame</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>number_of_employees</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>number_of_employees</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>number_of_employees</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>number_of_employees</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>goals_of_safety_measures</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>goals_of_safety_measures</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>safety_measures</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>safety_measures</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>employee_testing_results</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1103,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hotel_manager_forms_choices</t>
+          <t>safety_training_completed_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1120,7 +892,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hotel_manager_forms_choices</t>
+          <t>safety_training_completed_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1129,40 +901,6 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>safety_training_completed_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>safety_training_completed_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
